--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487655_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487655_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. VILLAMANDOS TORRES</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.901</v>
+        <v>4.107</v>
       </c>
       <c r="E2" t="n">
-        <v>1.802</v>
+        <v>1.7305</v>
       </c>
       <c r="F2" t="n">
-        <v>2.099</v>
+        <v>2.3765</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1479</v>
+        <v>-1.4821</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8875</v>
+        <v>-0.9961</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.0354</v>
+        <v>-0.4861</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.7468</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6436</v>
+        <v>-0.828</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6673</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1242</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2439</v>
+        <v>-0.1681</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3681</v>
+        <v>-0.5673</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7474</v>
+        <v>1.919</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7362</v>
+        <v>0.5535</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0112</v>
+        <v>1.3655</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8836</v>
+        <v>2.1179</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2239</v>
+        <v>2.1179</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>M. VILLAMANDOS TORRES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3937</v>
+        <v>3.0911</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6084000000000001</v>
+        <v>1.1829</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7853</v>
+        <v>1.9082</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.4821</v>
+        <v>-0.1479</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9961</v>
+        <v>1.8875</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4861</v>
+        <v>-2.0354</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7468</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.828</v>
+        <v>1.6436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.6673</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-1.1242</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1681</v>
+        <v>0.2439</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5673</v>
+        <v>-1.3681</v>
       </c>
       <c r="P3" t="n">
+        <v>-0.5821</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2.1344</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.5523</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.194</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.7463</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.2057</v>
+        <v>1.9375</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5687</v>
+        <v>1.1171</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7744</v>
+        <v>0.8205</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1179</v>
+        <v>1.8836</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1179</v>
+        <v>1.2239</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0324</v>
+        <v>2.3912</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7256</v>
+        <v>1.8459</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3068</v>
+        <v>0.5453</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4865</v>
+        <v>-3.3411</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5967</v>
+        <v>-1.9781</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0832</v>
+        <v>-1.363</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3106</v>
+        <v>-1.309</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9165</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.6059</v>
+        <v>-0.6623</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7971</v>
+        <v>-2.0321</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3198</v>
+        <v>-1.3314</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5227000000000001</v>
+        <v>-0.7008</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1344</v>
+        <v>-2.3284</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7164</v>
+        <v>3.1045</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9473</v>
+        <v>2.1413</v>
       </c>
       <c r="T4" t="n">
-        <v>1.421</v>
+        <v>1.1998</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5263</v>
+        <v>0.9416</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0105</v>
+        <v>2.8149</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1283</v>
+        <v>4.2836</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1388</v>
+        <v>-1.4686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1249</v>
+        <v>2.2565</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8249</v>
+        <v>0.3857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3</v>
+        <v>1.8707</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.3411</v>
+        <v>-0.4865</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9781</v>
+        <v>1.5967</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.363</v>
+        <v>-2.0832</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.309</v>
+        <v>0.3106</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6467000000000001</v>
+        <v>2.9165</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6623</v>
+        <v>-2.6059</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0321</v>
+        <v>-0.7971</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3314</v>
+        <v>-1.3198</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7008</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3284</v>
+        <v>-2.1344</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1045</v>
+        <v>2.7164</v>
       </c>
       <c r="S5" t="n">
-        <v>1.875</v>
+        <v>2.1714</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1787</v>
+        <v>1.0812</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6963</v>
+        <v>1.0902</v>
       </c>
       <c r="V5" t="n">
-        <v>2.8149</v>
+        <v>-0.0105</v>
       </c>
       <c r="W5" t="n">
-        <v>4.2836</v>
+        <v>1.1283</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4686</v>
+        <v>-1.1388</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0097</v>
+        <v>0.1914</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9235</v>
+        <v>0.1387</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9332</v>
+        <v>0.0527</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2965</v>
+        <v>0.4068</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8076</v>
+        <v>1.2243</v>
       </c>
       <c r="I6" t="n">
-        <v>0.511</v>
+        <v>-0.8175</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2325</v>
+        <v>1.0298</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3542</v>
+        <v>1.0298</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1218</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0641</v>
+        <v>-0.6231</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4533</v>
+        <v>0.1944</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3893</v>
+        <v>-0.8175</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.7761</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.1642</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-3.1045</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.9403</v>
+        <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3853</v>
+        <v>0.5608</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7433</v>
+        <v>0.2731</v>
       </c>
       <c r="U6" t="n">
-        <v>0.642</v>
+        <v>0.2877</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0851</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0384</v>
+        <v>0.1312</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6402</v>
+        <v>-0.5796</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6019</v>
+        <v>0.7109</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2393</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8129</v>
+        <v>0.9825</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5709</v>
+        <v>0.6314</v>
       </c>
       <c r="U7" t="n">
-        <v>0.242</v>
+        <v>0.3511</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2056</v>
+        <v>-0.2259</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.122</v>
+        <v>-1.7345</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08359999999999999</v>
+        <v>1.5087</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4068</v>
+        <v>-3.5971</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2243</v>
+        <v>-6.1436</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8175</v>
+        <v>2.5465</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0298</v>
+        <v>-1.765</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0298</v>
+        <v>-4.2058</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.4408</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6231</v>
+        <v>-1.8321</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1944</v>
+        <v>-1.9378</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8175</v>
+        <v>0.1056</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7761</v>
+        <v>-0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1642</v>
+        <v>-3.1045</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3881</v>
+        <v>2.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1637</v>
+        <v>1.6922</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0123</v>
+        <v>0.4051</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1514</v>
+        <v>1.287</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.8731</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.7298</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8567</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2755</v>
+        <v>-0.4373</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4167</v>
+        <v>-2.425</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1412</v>
+        <v>1.9877</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6214</v>
+        <v>-1.2965</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4706</v>
+        <v>-1.8076</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.092</v>
+        <v>0.511</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9927</v>
+        <v>-0.2325</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0092</v>
+        <v>-0.3542</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.002</v>
+        <v>0.1218</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6286</v>
+        <v>-1.0641</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4614</v>
+        <v>-1.4533</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.09</v>
+        <v>0.3893</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3881</v>
+        <v>-3.1045</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1519</v>
+        <v>1.9383</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0359</v>
+        <v>1.2418</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1878</v>
+        <v>0.6965</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.0851</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.4149</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4514</v>
+        <v>-0.7634</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0964</v>
+        <v>-1.0954</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6449</v>
+        <v>0.332</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5971</v>
+        <v>-1.6214</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.1436</v>
+        <v>1.4706</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5465</v>
+        <v>-3.092</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.765</v>
+        <v>-0.9927</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.2058</v>
+        <v>1.0092</v>
       </c>
       <c r="L10" t="n">
-        <v>2.4408</v>
+        <v>-2.002</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8321</v>
+        <v>-0.6286</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9378</v>
+        <v>0.4614</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1056</v>
+        <v>-1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.194</v>
+        <v>0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1045</v>
+        <v>-0.3881</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9105</v>
+        <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4666</v>
+        <v>0.664</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9567</v>
+        <v>0.2854</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4233</v>
+        <v>0.3785</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8731</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8099</v>
+        <v>-2.6587</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.181</v>
+        <v>-1.2205</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6289</v>
+        <v>-1.4381</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4342</v>
@@ -1312,13 +1312,13 @@
         <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1765</v>
+        <v>0.3278</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1828</v>
+        <v>0.1433</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0063</v>
+        <v>0.1845</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2553</v>
+        <v>-3.7493</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7013</v>
+        <v>-3.4405</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.554</v>
+        <v>-0.3087</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8302</v>
@@ -1390,13 +1390,13 @@
         <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6256</v>
+        <v>1.1317</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4621</v>
+        <v>0.7228</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1635</v>
+        <v>0.4088</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8567</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.425599999999998</v>
+        <v>4.3338</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.120199999999999</v>
+        <v>-5.211799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>9.5458</v>
+        <v>9.5459</v>
       </c>
       <c r="G13" t="n">
         <v>-18.0695</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.890600000000001</v>
+        <v>-5.8906</v>
       </c>
       <c r="I13" t="n">
         <v>-12.1789</v>
@@ -1444,10 +1444,10 @@
         <v>-6.4331</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1566999999999997</v>
+        <v>0.1567000000000008</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.5897</v>
+        <v>-6.589700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-11.6365</v>
@@ -1468,16 +1468,16 @@
         <v>17.463</v>
       </c>
       <c r="S13" t="n">
-        <v>14.5579</v>
+        <v>15.4665</v>
       </c>
       <c r="T13" t="n">
-        <v>6.746000000000001</v>
+        <v>7.654500000000001</v>
       </c>
       <c r="U13" t="n">
         <v>7.811900000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>7.907399999999999</v>
+        <v>7.907400000000001</v>
       </c>
       <c r="W13" t="n">
         <v>11.9999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9128</v>
+        <v>4.1191</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7569</v>
+        <v>3.857</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1559</v>
+        <v>0.2621</v>
       </c>
       <c r="G14" t="n">
         <v>6.0423</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4863</v>
+        <v>-1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0296</v>
+        <v>-0.9295</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4567</v>
+        <v>-0.3505</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7776</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9047</v>
+        <v>3.3535</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2921</v>
+        <v>2.3922</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6126</v>
+        <v>0.9613</v>
       </c>
       <c r="G15" t="n">
         <v>4.6529</v>
@@ -1624,13 +1624,13 @@
         <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5347</v>
+        <v>-1.086</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9085</v>
+        <v>-0.8084</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6263</v>
+        <v>-0.2776</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9896</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3917</v>
+        <v>2.2192</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5122</v>
+        <v>-0.4121</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9039</v>
+        <v>2.6314</v>
       </c>
       <c r="G16" t="n">
         <v>3.82</v>
@@ -1702,13 +1702,13 @@
         <v>2.7164</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.7283</v>
+        <v>-1.9008</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3325</v>
+        <v>-1.2324</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3959</v>
+        <v>-0.6684</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2821</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7982</v>
+        <v>1.4654</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1732</v>
+        <v>0.5093</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6251</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4295</v>
+        <v>4.491</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.145</v>
+        <v>0.2405</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5745</v>
+        <v>4.2505</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0406</v>
+        <v>3.8375</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.7827</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0406</v>
+        <v>3.0548</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3889</v>
+        <v>0.6535</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.145</v>
+        <v>-0.5421</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5339</v>
+        <v>1.1956</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5821</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3881</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.273</v>
+        <v>-1.6375</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1211</v>
+        <v>-1.0296</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1519</v>
+        <v>-0.6079</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2239</v>
+        <v>-0.6119</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2239</v>
+        <v>0.6119</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6045</v>
+        <v>0.88</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5093</v>
+        <v>0.1732</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.7068</v>
       </c>
       <c r="G18" t="n">
-        <v>4.491</v>
+        <v>0.4295</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2405</v>
+        <v>-0.145</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2505</v>
+        <v>0.5745</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8375</v>
+        <v>0.0406</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7827</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3.0548</v>
+        <v>0.0406</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6535</v>
+        <v>0.3889</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5421</v>
+        <v>-0.145</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1956</v>
+        <v>0.5339</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1344</v>
+        <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.4984</v>
+        <v>-0.1912</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0296</v>
+        <v>-0.1211</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4688</v>
+        <v>-0.0701</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6119</v>
+        <v>1.2239</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6119</v>
+        <v>1.2239</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2977</v>
+        <v>0.5919</v>
       </c>
       <c r="E19" t="n">
         <v>-0.3516</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6493</v>
+        <v>0.9435</v>
       </c>
       <c r="G19" t="n">
         <v>0.1337</v>
@@ -1936,13 +1936,13 @@
         <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6122</v>
+        <v>-0.318</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3634</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2488</v>
+        <v>0.0454</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2912</v>
+        <v>-0.0388</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9616</v>
+        <v>-3.8615</v>
       </c>
       <c r="F20" t="n">
-        <v>3.6704</v>
+        <v>3.8227</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3859</v>
@@ -2014,13 +2014,13 @@
         <v>2.7164</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7113</v>
+        <v>-1.4589</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3325</v>
+        <v>-1.2324</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3788</v>
+        <v>-0.2265</v>
       </c>
       <c r="V20" t="n">
         <v>1.2239</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8048</v>
+        <v>-1.5652</v>
       </c>
       <c r="E21" t="n">
         <v>-1.0921</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7127</v>
+        <v>-0.4731</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0951</v>
@@ -2092,13 +2092,13 @@
         <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.474</v>
+        <v>-1.2343</v>
       </c>
       <c r="T21" t="n">
         <v>-0.7268</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7472</v>
+        <v>-0.5075</v>
       </c>
       <c r="V21" t="n">
         <v>-1.788</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8562</v>
+        <v>-2.7472</v>
       </c>
       <c r="E22" t="n">
         <v>-0.7672</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0889</v>
+        <v>-1.9799</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4082</v>
@@ -2170,13 +2170,13 @@
         <v>0.7761</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7763</v>
+        <v>-0.6673</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5946</v>
+        <v>-0.4856</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4477</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2519</v>
+        <v>-3.094</v>
       </c>
       <c r="E23" t="n">
         <v>-2.4141</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8378</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>1.075</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1045</v>
+        <v>-0.9466</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3634</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7411</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.894</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.131</v>
+        <v>-5.9402</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8485</v>
+        <v>-7.2489</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7175</v>
+        <v>1.3087</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6856</v>
@@ -2326,13 +2326,13 @@
         <v>1.5523</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3589</v>
+        <v>-1.1681</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4229</v>
+        <v>-0.8233</v>
       </c>
       <c r="U24" t="n">
-        <v>0.064</v>
+        <v>-0.3448</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5642</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.425499999999999</v>
+        <v>-0.7562999999999986</v>
       </c>
       <c r="E25" t="n">
         <v>-9.2158</v>
       </c>
       <c r="F25" t="n">
-        <v>5.790500000000001</v>
+        <v>8.459700000000002</v>
       </c>
       <c r="G25" t="n">
         <v>18.0696</v>
@@ -2404,13 +2404,13 @@
         <v>18.4331</v>
       </c>
       <c r="S25" t="n">
-        <v>-14.5579</v>
+        <v>-11.8887</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.812000000000001</v>
+        <v>-7.812</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.746099999999999</v>
+        <v>-4.0767</v>
       </c>
       <c r="V25" t="n">
         <v>-7.907300000000001</v>
